--- a/dados-modelo-impacto/processed/consolidado_impacto_resultados.xlsx
+++ b/dados-modelo-impacto/processed/consolidado_impacto_resultados.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teste de sinal por zona. 0-0,5 km: 12/14, p=0,0065, excesso mediano +2,06 p.p. Some em 1-2 km (8/14, p=0,395).</t>
+          <t>Teste de sinal por zona. 0-0,5 km: 12/14, p=0,0065, excesso mediano +2,06 p.p. ATENCAO: essa zona e um DISCO e inclui o predio do data center. Descontando o footprint o excesso cai para +1,50 p.p., com os mesmos 12/14 e o mesmo p — e e esse o numero que deve ser citado. Some em 1-2 km (8/14, p=0,395).</t>
         </is>
       </c>
     </row>
